--- a/gsap_self_study.xlsx
+++ b/gsap_self_study.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="gsap_self_study" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gsap_self_study" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'gsap_self_study'!$A$1:$S$143</definedName>
@@ -1001,9 +1001,21 @@
           <t>01-tweens</t>
         </is>
       </c>
-      <c r="Q6" s="4" t="n"/>
-      <c r="R6" s="4" t="n"/>
-      <c r="S6" s="4" t="n"/>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>fromTo = explicit start + end, so replay snaps to the same start state every click (from-vars hold ONLY start values; duration/ease/overwrite live in TO vars). Spam-click looked fine even without overwrite because the newest tween renders last and wins; the real need shows when an older tween OUTLIVES the newer one: A (x:300, 3s) then B (x:0, 0.4s) without overwrite -&gt; box returns to 0 then creeps back to 300 (zombie tween, onInterrupt never fires). overwrite:true on B kills tween A entirely (onInterrupt fires); overwrite:'auto' kills only the overlapping property (x) so A's rotation keeps going. Rule: true = kill the whole conflicting tween, 'auto' = kill only shared properties, default false = tweens stack and fight. Misses: misspelled vars key (overWrite) = 'Invalid property' warning, silently ignored (silent-failure family); handlers that CREATE tweens must be wrapped in contextSafe (3rd repeat). Lab: practice/src/app/lessons/tweens/lesson5</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -1078,9 +1090,21 @@
           <t>01-tweens</t>
         </is>
       </c>
-      <c r="Q7" s="4" t="n"/>
-      <c r="R7" s="4" t="n"/>
-      <c r="S7" s="4" t="n"/>
+      <c r="Q7" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>5 cards hidden on load, one Reveal button toggles them. gsap.set() = instant values only; gave it duration again (regression on the 2026-07-02 miss). FLASH LESSON: no GSAP call can stop a load flash — Next.js server-renders the cards visible, the browser paints, THEN JS hydrates and useGSAP runs (even as a layout effect it is after first paint). So CSS must own the pre-JS hidden state: Tailwind `invisible` (visibility:hidden) on the cards; `hidden` (display:none) is the WRONG channel because autoAlpha only touches opacity + visibility. The set(autoAlpha:0) is still needed: the class sets only visibility, so without set the .to reads opacity 1 as start and just pops instead of fading — who else writes to this channel. Reveal = ONE gsap.to(autoAlpha:1, paused:true) built once inside useGSAP (scope) and stored in a useRef; button handler only play()/reverse() so no contextSafe (steer, not create). paused:true = build the tween but do not start the clock; without it the tween auto-played on mount and the first click HID the cards. Misses: typo `opactiy` (Invalid property, silent), duration on set, scope arg dropped off useGSAP again, wrapped a steer-only handler in contextSafe (react-hooks/refs lint error). Lab: practice/src/app/lessons/tweens/lesson6</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -1151,9 +1175,21 @@
         <v>1.5</v>
       </c>
       <c r="P8" s="3" t="n"/>
-      <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="n"/>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>DOOR: one paused gsap.to(rotationY:120, transformPerspective:800, transformOrigin:'left', power2.inOut, 0.8s) stored in a ref, button toggles play/reverse. transformOrigin = the hinge (default spins around center); transformPerspective on the element = depth (without it a rotationY looks like a horizontal squash); 180deg is a card flip not a door, ~100-120 reads as a door; reverse() plays the ease curve BACKWARDS so an .out ease closes like an .in (hesitate then slam) -&gt; use inOut for anything that toggles along the same path, or timeScale the reverse. BADGE: anchor + badge both absolute top/left 50% (percent of PARENT) -&gt; their top-left CORNER sits on center; set(xPercent:-50, yPercent:-50) (percent of OWN size) pulls the middle onto the anchor for ANY element size. x:150 tween slides the badge and it stays on the dot's row: x/y and xPercent/yPercent are separate channels. Dot stays fixed on purpose as the reference. Positioning flicker on reload = task-6 flash again (set runs after first paint) but the pre-JS state here is a TRANSFORM so a Tailwind -translate class would be the channel clash from the 2026-07-13 row; fix = Tailwind `invisible` + the same set also does autoAlpha:1 -&gt; elements appear already centered. Misses: paused put on a set instead of the tween; vars object built but not passed; top/left -50% instead of +50% (confused with xPercent -50); reached for translate-[50%] to center (own-size not parent); second useGSAP/contextSafe on a steer-only page. Lab: practice/src/app/lessons/tweens/lesson7</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -1224,9 +1260,21 @@
         <v>1.5</v>
       </c>
       <c r="P9" s="3" t="n"/>
-      <c r="Q9" s="4" t="n"/>
-      <c r="R9" s="4" t="n"/>
-      <c r="S9" s="4" t="n"/>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>Control panel (play/pause/reverse/restart/slow/2x) on ONE stored tween: gsap.to(x:800, rotation:360, 3s, ease none, paused:true) built once inside useGSAP (scope) and held in useRef&lt;gsap.core.Tween&gt;(null); every button = plain handler calling one method on it, no contextSafe (steer not create). Experiments: (1) play after the tween finished does NOTHING (play = run toward the end from here; at the end nowhere to go) -&gt; restart = jump to 0 then play. (2) GSAP 3 GOTCHA: reversed is NOT a separate flag, it is the SIGN of timeScale — reverse() makes timeScale negative, so timeScale(2) while reversing silently flipped the box FORWARD. Fix: preserve direction by setting Math.sign(t.timeScale()) * speed (sign = direction, constant = speed); my first attempts multiplied by the whole current value (compounded 0.5-&gt;0.25) and negated in an else branch (flipped direction again). (3) pause freezes the playhead, reverse from a pause resumes backward from that spot. (4) timeScale STICKS through restart — restart resets the playhead not the speed; reset to 1 in the restart branch if you want 'from start at normal speed'. Also: yoyo without repeat is a silent no-op (GSAP does not warn). Lab: practice/src/app/lessons/tweens/lesson8</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">

--- a/gsap_self_study.xlsx
+++ b/gsap_self_study.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gsap_self_study" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="gsap_self_study" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'gsap_self_study'!$A$1:$S$143</definedName>
@@ -1345,9 +1345,21 @@
         <v>1</v>
       </c>
       <c r="P10" s="3" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-      <c r="R10" s="4" t="n"/>
-      <c r="S10" s="4" t="n"/>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>Loading bar: .progress scaleX 0 -&gt; 1 (origin-left) over 2s ease none. onUpdate: function () { setLabel(Math.round(this.progress() * 100)) } -&gt; label 0..100 every frame; onComplete: () =&gt; setIsDisabled(false) unlocks the Next button (disabled: variant shows the locked state). Learned: (1) callbacks take a FUNCTION not a call; (2) onUpdate fires once per FRAME so +1 per call counts frames (~240 at 60Hz) - read progress() instead; (3) `this` is the tween only in a regular function - arrow functions have no own this (callbackScope) - or read it from a stored ref; (4) scaleX is a unitless multiplier (1 = full) vs width '100%'; scaleX squashes rounded corners, width doesn't. Lab: practice/src/app/lessons/tweens/lesson9</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -1418,9 +1430,21 @@
         <v>1</v>
       </c>
       <c r="P11" s="3" t="n"/>
-      <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
-      <c r="S11" s="4" t="n"/>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>3 demos: (1) rocket floats forever - y:-20 duration 1.5 repeat:-1 yoyo sine.inOut (positive y = DOWN); (2) NEW badge pulses exactly 3x - scale 1.2 duration 0.5 repeat:5 yoyo -&gt; with yoyo pulses = (repeat+1)/2 and an EVEN play count ends at normal size; (3) box jumps to a new random spot each cycle - x/y 'random(-200,200)' STRING + repeatRefresh:true + repeatDelay 0.5, no yoyo. Learned: Math.random() is computed once by JS before GSAP sees it so repeatRefresh has nothing to re-roll; the random() string (or a function) is re-evaluated each repeat, and repeatRefresh also re-records the start so it jumps from where it is. Also hit: items-enter typo = silent no-op. Lab: practice/src/app/lessons/tweens/lesson10</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -1491,9 +1515,21 @@
         <v>1</v>
       </c>
       <c r="P12" s="3" t="n"/>
-      <c r="Q12" s="4" t="n"/>
-      <c r="R12" s="4" t="n"/>
-      <c r="S12" s="4" t="n"/>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>(1) Scatter: ONE gsap.to('.dot') with x/y: () =&gt; gsap.utils.random(-200, 200) - GSAP calls the function once per target so all 12 dots land differently; function args are (index, target, targets) - index is for PATTERNS. A function must RETURN A NUMBER: returning the 'random()' string is never parsed. (2) Arrows: data array {label, property, amount '+=100'/'-=100'} + ONE handler using a computed key [property]: amount; each click CREATES a new tween so it is wrapped in contextSafe (CREATE vs STEER: a stored tween's += is recorded once, so restart() would never accumulate). Relative values add to wherever the box is NOW, so fast clicks can land off the 100px grid. One useGSAP per component: const { contextSafe } = useGSAP(fn, { scope }); contextSafe takes one arg; use scoped '.box' instead of ref.current in handlers (react-hooks/refs lint). Lab: practice/src/app/lessons/tweens/lesson11</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
@@ -1564,9 +1600,21 @@
         <v>1</v>
       </c>
       <c r="P13" s="3" t="n"/>
-      <c r="Q13" s="4" t="n"/>
-      <c r="R13" s="4" t="n"/>
-      <c r="S13" s="4" t="n"/>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>Theme toggle: ONE paused gsap.to(document.documentElement, { '--background', '--foreground', '--card', '--button-foreground': dark hex, duration 0.8 }) stored in a ref; button toggles play()/reverse() (STEER -&gt; no contextSafe). GSAP writes the vars as inline style on &lt;html&gt; which beats :root in globals.css, and useGSAP reverts them on unmount. Gradient: bg-linear-to-r from-(--g1) to-(--g2) + a 2nd unpaused tween on &lt;html&gt; animating only --g1/--g2 with repeat:-1 yoyo (different vars -&gt; the two tweens don't fight). Learned: animate the VARIABLE not each element; each Tailwind color needs :root value + @theme --color-name (class is bg-name); GSAP animates the :root names not --color-*; values must be real CSS colors (hex) not class names; &lt;html&gt; is outside the scope so pass the element not a selector. Lab: practice/src/app/lessons/tweens/lesson12</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1641,9 +1689,21 @@
           <t>14-text-fx</t>
         </is>
       </c>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="n"/>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>GSAP tweens ANY number on ANY object: gsap.to(obj, { value: 1000 }) - the key is just the object's property name (non-setting keys = properties to animate). Ref version: obj in useRef({value:0}), onUpdate writes Math.round(obj.value) into span.textContent -&gt; 1 render total. State version: same object + onUpdate calls setCount(round) -&gt; ~240 re-renders in 4s (60fps x 4). React state can't be tweened directly - only via the setter. Round (or snap:{value:1}) or decimals flicker; tabular-nums stops digit wobble. Durations are SECONDS. Missed: kept passing the span as the target while reading the object (stuck at 0); useRef(count) = bare number; gsap.to('') ; duration 4000; stale countRef guard / ref in the other component.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
@@ -1714,9 +1774,21 @@
         <v>1</v>
       </c>
       <c r="P15" s="3" t="n"/>
-      <c r="Q15" s="4" t="n"/>
-      <c r="R15" s="4" t="n"/>
-      <c r="S15" s="4" t="n"/>
+      <c r="Q15" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>Click-follow box: contextSafe handler creates gsap.to('.box' {x y}) per click; centre = clientX - rect.left - half size. overwrite:false (default) = old tweens keep writing the same props; hidden while the newest ends last, visible when a newer SHORT tween ends before an older LONG one (box drifts back) - reproduced with e.shiftKey ? 0.3 : 3 + ease none. overwrite:'auto' kills only overlapping props (mount rotation survives); overwrite:true kills EVERY tween on the target (rotation died). gsap.killTweensOf(el 'x,y') = manual stop with no new tween (Stop button + stopPropagation); tween.kill() when you hold a ref; isTweening is always true with an endless tween running. Missed: identical tweens hid the bug; -80/+80 centering; rotation inside click tween; 6th double-useGSAP slip.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
@@ -1791,9 +1863,21 @@
           <t>02-easing</t>
         </is>
       </c>
-      <c r="Q16" s="4" t="n"/>
-      <c r="R16" s="4" t="n"/>
-      <c r="S16" s="4" t="n"/>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>Ease race in lessons/ease/lesson15: families x variants arrays build 'family.variant' strings; nested map renders lanes (label + track + dot with data-ease); one useGSAP forEach -&gt; one tween per dot via [data-ease="..."] scoped selector; x = track width - dot width (function-based). Seen: .out = fast start + brakes at the end; power1-&gt;power4-&gt;expo = stronger curve; back.in pulls behind the start / back.out overshoots the end; bounce.out = ball landing. RULE - where does it END? entering/on screen -&gt; .out (modal dropdown); exiting/off screen -&gt; .in (toast deleted item); visible A-&gt;B -&gt; .inOut (carousel). '.out' sounds like leaving but means the braking is at the END. Missed: tag vs attribute selectors; one tween hitting every dot; document.querySelector skips scope; props object not unpacked; dotted class names; couldn't pick variants at first.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
@@ -1868,9 +1952,21 @@
           <t>02-easing</t>
         </is>
       </c>
-      <c r="Q17" s="4" t="n"/>
-      <c r="R17" s="4" t="n"/>
-      <c r="S17" s="4" t="n"/>
+      <c r="Q17" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>Part A: buttonArr { label color easeIn easeOut } mapped (key) -&gt; one contextSafe hoverScale(e ease isIn): scale isIn ? 1.5 : 1 + overwrite:'auto' on e.currentTarget; hover-out .out (ends on screen). back.out(n): n = overshoot (1.2 subtle / 4 strong). elastic.out(amplitude period): amplitude = wobble size (2 &gt; 1); smaller period = faster wiggles (0.1 jittery / 0.3-0.6 smooth) - give elastic time to show. Part B: rpgsprites1 sheet = 3 cols x 4 rows of 32x36 (rows: 0 up / -36 right / -72 down / -108 left). Window w-8 h-9 + bg-[url(...)] + zoom-[4] + [image-rendering:pixelated]. backgroundPosition 'X Y' -&gt; '-96px -36px' + steps(3) + repeat -1: steps = frame count and distance = frameW x frames (steps(2) glitch / steps(6) jitter / no ease = sliding). Walk: second tween x on .walker (full-width parent!) ease none so body speed matches the constant steps; row must face the travel direction or he moonwalks.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
@@ -1945,9 +2041,21 @@
         <v>1</v>
       </c>
       <c r="P18" s="3" t="n"/>
-      <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="n"/>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>CustomEase registered + created ONCE in @/lib/gsap: CustomEase.create('popup', '.66,.38,.48,.98') - just the 4 cubic-bezier numbers (or SVG path data 'M0,0 C...'); the CSS 'cubic-bezier(...)' wrapper throws 'malformed path' and breaks every lesson importing the lib. gsap.defaults({ ease: 'popup' }) right AFTER create -&gt; every tween without its own ease uses it app-wide (old lessons changed feel too); a tween's own ease overrides the default. Without defaults GSAP silently uses power1.out. popup = slow start / fast middle / soft landing (~19% at 25% time). Lesson 17: blue power2.out vs yellow default popup doing x + rotate + scale + autoAlpha (opacity-0 class to avoid flash).</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
@@ -2022,9 +2130,21 @@
         <v>1</v>
       </c>
       <c r="P19" s="3" t="n"/>
-      <c r="Q19" s="4" t="n"/>
-      <c r="R19" s="4" t="n"/>
-      <c r="S19" s="4" t="n"/>
+      <c r="Q19" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>Shake: CustomWiggle.create('shake' { wiggles: 5 type: 'easeOut' }) once in @/lib/gsap; ease goes 0 -&gt; 1 -&gt; -1 -&gt; ... -&gt; 0 so x: 10 = shake SIZE and it ends at the start. Wrong password -&gt; gsap.fromTo('.inputShake' { x: 0 } { x: 10 ease: 'shake' duration 0.6 overwrite auto }) - fromTo so spammed Enter never drifts. Ball: CustomBounce.create('ballBounce' { strength 0-1 squash squashID: 'ballBounce-squash' }) builds TWO curves from the same settings; one tween per curve (one tween = one ease): y: 176 with ballBounce + scaleX 1.4 / scaleY 0.6 with ballBounce-squash and transformOrigin 'center bottom'; shared timing object { duration repeat repeatDelay } keeps them synced. strength = bounciness / squash setting = floor contact time / tween scale values = how flat. Track h-64 border-b-4 items-start so 256 - 80 = 176 lands on the floor. Wiggle/Bounce create() only in the browser (typeof window check): on the server GSAP only queues plugins -&gt; 'yEase is not a function'.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
@@ -2099,9 +2219,21 @@
         <v>1</v>
       </c>
       <c r="P20" s="3" t="n"/>
-      <c r="Q20" s="4" t="n"/>
-      <c r="R20" s="4" t="n"/>
-      <c r="S20" s="4" t="n"/>
+      <c r="Q20" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>EasePack: import { RoughEase } from 'gsap/EasePack' + registerPlugin -&gt; also registers 'slow' and 'expoScale'; used by name, no create() and no window guard. Flicker title: autoAlpha 1 + x 5 with `rough({ points: 30 strength: 2 template: power2.out taper: out randomize: true clamp: true })` - backtick string for multi-line, NO trailing comma (GSAP parses the text itself), quotes optional. taper out = calms then stays on; randomize = glitch vs strobe; clamp keeps jitter inside 0-1. Rough still ENDS at the end value (wiggle returns to start). Zoom 1-&gt;50: eye judges RATIOS (1-&gt;2 = x2 / 49-&gt;50 = +2%) so ease none bursts then crawls; expoScale(1,50) = equal ratio per moment = looks constant; numbers must match the tween's scales (optional 3rd base ease). Demo: tiny unfilled ring (h-6 border-4) inside its OWN overflow-hidden window; 3s shared timing. slow(0.7,0.7) = fast / hang in the middle / fast (bullet time).</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">

--- a/gsap_self_study.xlsx
+++ b/gsap_self_study.xlsx
@@ -2308,9 +2308,21 @@
           <t>04-stagger</t>
         </is>
       </c>
-      <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="n"/>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>Version A = stagger: { amount: 1 } -&gt; TOTAL spread of start times is 1s so the 5th and the 50th box both START at the 1s mark (gap = 1/(n-1)). Version B = stagger: { each: 0.1 } -&gt; FIXED gap per item so 5 items = 0.4s wave, 50 items = 4.9s. A bare number (stagger: 0.1) is shorthand for each. Proved with a count state (5 / 50 buttons) + dependencies: [count] on useGSAP so the tween re-runs on the new boxes. Used gsap.fromTo (explicit start y:-100 autoAlpha:0) because 50 -&gt; 5 reuses the first five DOM nodes which already sit at the end values - gsap.to had nowhere to go. Stagger gap != tween duration: each item still takes its own 0.5s.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
@@ -2385,9 +2397,21 @@
           <t>04-stagger</t>
         </is>
       </c>
-      <c r="Q22" s="4" t="n"/>
-      <c r="R22" s="4" t="n"/>
-      <c r="S22" s="4" t="n"/>
+      <c r="Q22" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>Ripple: row of 15 dots; click handler wrapped in contextSafe (config-only useGSAP({ scope }) is valid when there is no mount tween - ONE call per component is the rule). gsap.to('.box' { scale: 0.1 repeat: 1 yoyo: true stagger: { from: index amount: 1 ease } }) - from: &lt;index&gt; makes the clicked dot start first and the wave spreads BOTH ways; from: 'center' / 'edges' / 'start' are the named origins. yoyo needs repeat or the dots just shrink and stay. amount: 1 keeps the whole ripple at 1s from any origin. Stagger ease (inside the stagger object) shapes the GAPS between start times; the tween ease shapes each dot's own motion - two separate clocks. axis only matters with grid (lesson 22). overwrite: 'auto' (lowercase) stops rapid clicks stacking scale tweens.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
@@ -2462,9 +2486,21 @@
           <t>04-stagger</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="n"/>
-      <c r="S23" s="4" t="n"/>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>10x10 tile wall (Array.from 100 + grid-cols-10) so DOM order = visual rows. Same handler shape as lab 21 (contextSafe, from: index, amount: 1, repeat 1 + yoyo, overwrite 'auto' lowercase). grid: [10, 10] (rows, cols; or 'auto' = GSAP measures the layout) makes from: index mean 'the tile at that grid position' and every other tile's delay = straight-line distance from it -&gt; ring from the centre, quarter-circle from a corner, far corner last, diagonal arrives with the straight lines. Without grid the same from: index snakes row by row in DOM order. axis: 'x' = distance measured horizontally only -&gt; the clicked COLUMN moves first and the wave sweeps left/right; axis: 'y' = row sweep. axis is ignored without grid. Verified circle + corner; axis variant tested by toggling the key (left commented for the 2D default).</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
@@ -2535,9 +2571,21 @@
         <v>1</v>
       </c>
       <c r="P24" s="3" t="n"/>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="n"/>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>done</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>Fan of 7 absolute cards (relative wrapper, origin-bottom) from ONE gsap.to('.card'). distribute returns a FUNCTION (i, target, arr) -&gt; value; pass the function itself as the property value - GSAP calls it per card. Config keys: base, amount, each, from, ease, grid, axis (there is NO end). base = value at the from position, base + amount = value at the farthest card, so -30 to 30 = base -30 amount 60 (default from start). from: 'center' hands BASE to the middle card so with base 0.9 the centre was the SMALLEST - fixed with from: 'edges' (edges get base, centre gets base + amount). Stagger amount: 1 unfolds the fan; replay = stored tween in a ref + play/reverse toggle (steer only, no contextSafe). Changing 7 -&gt; 9 still fans evenly with no code change. 'random(-30,30)' = scatter (unrelated per-card values), distribute = evenly SPACED values.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
